--- a/docs/d/212/inyear.xlsx
+++ b/docs/d/212/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 59 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 56 clubs short</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -906,8 +906,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -9830,8 +9830,8 @@
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA94" s="10" t="n">
         <v>1</v>
@@ -10051,7 +10051,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10121,8 +10121,8 @@
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="9" t="n">
-        <v>0</v>
+      <c r="Z97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -13029,7 +13029,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -13623,7 +13623,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13656,7 +13656,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>

--- a/docs/d/212/inyear.xlsx
+++ b/docs/d/212/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/212/inyear.xlsx
+++ b/docs/d/212/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 8 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 8 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 56 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 54 clubs short</t>
         </is>
       </c>
     </row>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L43" s="8" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -5169,7 +5169,7 @@
         <v>0</v>
       </c>
       <c r="X46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y46" s="9" t="n">
         <v>0</v>
@@ -7379,7 +7379,7 @@
         <v>0</v>
       </c>
       <c r="Q69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" s="9" t="n">
         <v>0</v>
@@ -9372,7 +9372,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9442,8 +9442,8 @@
       <c r="Y90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" s="9" t="n">
-        <v>0</v>
+      <c r="Z90" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="AA90" s="10" t="n">
         <v>1</v>
@@ -9663,7 +9663,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -9715,8 +9715,8 @@
       <c r="S93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T93" s="9" t="n">
-        <v>0</v>
+      <c r="T93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U93" s="9" t="n">
         <v>0</v>
@@ -12061,8 +12061,8 @@
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="9" t="n">
-        <v>0</v>
+      <c r="Z117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA117" s="9" t="n">
         <v>0</v>
@@ -13590,7 +13590,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13623,7 +13623,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>

--- a/docs/d/212/inyear.xlsx
+++ b/docs/d/212/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 8 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 8 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 54 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 38 clubs short</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
         <v>0</v>
       </c>
       <c r="X5" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y5" s="9" t="n">
         <v>0</v>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1682,8 +1682,8 @@
       <c r="Y10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="9" t="n">
-        <v>0</v>
+      <c r="Z10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA10" s="10" t="n">
         <v>1</v>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3137,8 +3137,8 @@
       <c r="Y25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" s="9" t="n">
-        <v>0</v>
+      <c r="Z25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA25" s="10" t="n">
         <v>1</v>
@@ -3649,7 +3649,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3719,8 +3719,8 @@
       <c r="Y31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z31" s="9" t="n">
-        <v>0</v>
+      <c r="Z31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA31" s="10" t="n">
         <v>1</v>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>0</v>
@@ -4301,8 +4301,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4495,8 +4495,8 @@
       <c r="Y39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z39" s="9" t="n">
-        <v>0</v>
+      <c r="Z39" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA39" s="10" t="n">
         <v>1</v>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -4883,8 +4883,8 @@
       <c r="Y43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" s="9" t="n">
-        <v>0</v>
+      <c r="Z43" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA43" s="10" t="n">
         <v>1</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="X44" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y44" s="9" t="n">
         <v>0</v>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5077,8 +5077,8 @@
       <c r="Y45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z45" s="9" t="n">
-        <v>0</v>
+      <c r="Z45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA45" s="10" t="n">
         <v>1</v>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5271,8 +5271,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -5342,7 +5342,7 @@
         <v>0</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" s="9" t="n">
         <v>0</v>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -5932,8 +5932,8 @@
       <c r="S54" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T54" s="9" t="n">
-        <v>0</v>
+      <c r="T54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U54" s="9" t="n">
         <v>0</v>
@@ -6333,7 +6333,7 @@
         <v>0</v>
       </c>
       <c r="X58" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y58" s="9" t="n">
         <v>0</v>
@@ -6527,7 +6527,7 @@
         <v>0</v>
       </c>
       <c r="X60" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y60" s="9" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6629,8 +6629,8 @@
       <c r="Y61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z61" s="9" t="n">
-        <v>0</v>
+      <c r="Z61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA61" s="10" t="n">
         <v>1</v>
@@ -6818,7 +6818,7 @@
         <v>8</v>
       </c>
       <c r="X63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y63" s="9" t="n">
         <v>0</v>
@@ -7182,7 +7182,7 @@
         </is>
       </c>
       <c r="P67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q67" s="9" t="n">
         <v>0</v>
@@ -7197,7 +7197,7 @@
         <v>1</v>
       </c>
       <c r="U67" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V67" s="9" t="n">
         <v>2</v>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8278,8 +8278,8 @@
       <c r="Y78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" s="9" t="n">
-        <v>0</v>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA78" s="10" t="n">
         <v>1</v>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -8569,8 +8569,8 @@
       <c r="Y81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z81" s="9" t="n">
-        <v>0</v>
+      <c r="Z81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA81" s="10" t="n">
         <v>1</v>
@@ -8758,7 +8758,7 @@
         <v>0</v>
       </c>
       <c r="X83" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y83" s="9" t="n">
         <v>0</v>
@@ -8855,7 +8855,7 @@
         <v>0</v>
       </c>
       <c r="X84" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y84" s="9" t="n">
         <v>0</v>
@@ -8887,7 +8887,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -8957,8 +8957,8 @@
       <c r="Y85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z85" s="9" t="n">
-        <v>0</v>
+      <c r="Z85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA85" s="10" t="n">
         <v>1</v>
@@ -9081,7 +9081,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9151,8 +9151,8 @@
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="9" t="n">
-        <v>0</v>
+      <c r="Z87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA87" s="10" t="n">
         <v>1</v>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9230,8 +9230,8 @@
       <c r="S88" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T88" s="9" t="n">
-        <v>0</v>
+      <c r="T88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U88" s="9" t="n">
         <v>0</v>
@@ -9469,7 +9469,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -9539,8 +9539,8 @@
       <c r="Y91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z91" s="9" t="n">
-        <v>0</v>
+      <c r="Z91" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA91" s="10" t="n">
         <v>1</v>
@@ -9728,7 +9728,7 @@
         <v>0</v>
       </c>
       <c r="X93" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y93" s="9" t="n">
         <v>0</v>
@@ -10115,8 +10115,8 @@
       <c r="W97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X97" s="9" t="n">
-        <v>3</v>
+      <c r="X97" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y97" s="9" t="n">
         <v>0</v>
@@ -11312,7 +11312,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11382,8 +11382,8 @@
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="9" t="n">
-        <v>0</v>
+      <c r="Z110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA110" s="10" t="n">
         <v>1</v>
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11576,8 +11576,8 @@
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -11849,8 +11849,8 @@
       <c r="S115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T115" s="9" t="n">
-        <v>0</v>
+      <c r="T115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U115" s="9" t="n">
         <v>0</v>
@@ -12637,8 +12637,8 @@
       <c r="W123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X123" s="9" t="n">
-        <v>2</v>
+      <c r="X123" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
@@ -13062,7 +13062,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -13161,7 +13161,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -13194,7 +13194,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -13227,7 +13227,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -13260,7 +13260,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -13293,7 +13293,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -13359,7 +13359,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -13392,7 +13392,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13491,7 +13491,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13524,7 +13524,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13557,7 +13557,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13590,7 +13590,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13722,7 +13722,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>

--- a/docs/d/212/inyear.xlsx
+++ b/docs/d/212/inyear.xlsx
@@ -103,8 +103,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 8 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 8 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 38 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 38 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,20 +850,20 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M2" s="7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -871,7 +871,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O2" s="8" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -947,20 +947,20 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" s="8" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M3" s="7" t="n">
+      <c r="M3" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -968,7 +968,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -992,7 +992,7 @@
         <v>0</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1044,20 +1044,20 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M4" s="7" t="n">
+      <c r="M4" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -1065,7 +1065,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1141,20 +1141,20 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -1162,7 +1162,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O5" s="8" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1246,12 +1246,12 @@
       <c r="K6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="8" t="inlineStr">
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M6" s="7" t="n">
+      <c r="M6" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -1259,7 +1259,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1335,20 +1335,20 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M7" s="7" t="n">
+      <c r="M7" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -1356,7 +1356,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1432,20 +1432,20 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M8" s="7" t="n">
+      <c r="M8" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -1453,7 +1453,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O8" s="8" t="inlineStr">
+      <c r="O8" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1529,20 +1529,20 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M9" s="7" t="n">
+      <c r="M9" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -1550,7 +1550,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="O9" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1626,20 +1626,20 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="M10" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -1647,7 +1647,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O10" s="8" t="inlineStr">
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1723,20 +1723,20 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M11" s="7" t="n">
+      <c r="M11" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1744,7 +1744,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O11" s="8" t="inlineStr">
+      <c r="O11" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1820,20 +1820,20 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M12" s="7" t="n">
+      <c r="M12" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1841,7 +1841,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1925,12 +1925,12 @@
       <c r="K13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="8" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M13" s="7" t="n">
+      <c r="M13" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1938,7 +1938,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2014,20 +2014,20 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M14" s="7" t="n">
+      <c r="M14" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -2035,7 +2035,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2111,20 +2111,20 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M15" s="7" t="n">
+      <c r="M15" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -2132,7 +2132,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2208,20 +2208,20 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -2229,7 +2229,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2246,8 +2246,8 @@
       <c r="S16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T16" s="9" t="n">
-        <v>0</v>
+      <c r="T16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U16" s="9" t="n">
         <v>0</v>
@@ -2313,12 +2313,12 @@
       <c r="K17" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L17" s="8" t="inlineStr">
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M17" s="7" t="n">
+      <c r="M17" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -2326,7 +2326,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2341,7 +2341,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T17" s="10" t="n">
         <v>1</v>
@@ -2410,12 +2410,12 @@
       <c r="K18" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="L18" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M18" s="7" t="n">
+      <c r="M18" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -2423,7 +2423,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2499,20 +2499,20 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M19" s="7" t="n">
+      <c r="M19" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -2520,7 +2520,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2596,20 +2596,20 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M20" s="7" t="n">
+      <c r="M20" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -2617,7 +2617,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2693,20 +2693,20 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M21" s="7" t="n">
+      <c r="M21" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2714,7 +2714,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O21" s="8" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2790,20 +2790,20 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M22" s="7" t="n">
+      <c r="M22" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2811,7 +2811,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2887,20 +2887,20 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M23" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2908,7 +2908,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2932,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
@@ -2997,7 +2997,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M24" s="7" t="n">
+      <c r="M24" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -3005,7 +3005,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O24" s="8" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3081,20 +3081,20 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M25" s="7" t="n">
+      <c r="M25" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -3102,7 +3102,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O25" s="8" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3178,20 +3178,20 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M26" s="7" t="n">
+      <c r="M26" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -3199,7 +3199,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O26" s="8" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3275,20 +3275,20 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L27" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M27" s="7" t="n">
+      <c r="M27" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -3296,7 +3296,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O27" s="8" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3372,20 +3372,20 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
+        <v>-15</v>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M28" s="7" t="n">
+      <c r="M28" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -3393,7 +3393,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O28" s="8" t="inlineStr">
+      <c r="O28" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3469,20 +3469,20 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L29" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M29" s="7" t="n">
+      <c r="M29" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -3490,7 +3490,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O29" s="8" t="inlineStr">
+      <c r="O29" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3566,20 +3566,20 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M30" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -3587,7 +3587,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O30" s="8" t="inlineStr">
+      <c r="O30" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3663,20 +3663,20 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M31" s="7" t="n">
+      <c r="M31" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3684,7 +3684,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O31" s="8" t="inlineStr">
+      <c r="O31" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3760,20 +3760,20 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M32" s="7" t="n">
+      <c r="M32" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3781,7 +3781,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O32" s="8" t="inlineStr">
+      <c r="O32" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3805,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>0</v>
@@ -3865,12 +3865,12 @@
       <c r="K33" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L33" s="8" t="inlineStr">
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M33" s="7" t="n">
+      <c r="M33" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -3878,7 +3878,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O33" s="8" t="inlineStr">
+      <c r="O33" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3954,20 +3954,20 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L34" s="8" t="inlineStr">
+        <v>-17</v>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M34" s="7" t="n">
+      <c r="M34" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -3975,7 +3975,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O34" s="8" t="inlineStr">
+      <c r="O34" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4051,20 +4051,20 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M35" s="7" t="n">
+      <c r="M35" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -4072,7 +4072,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O35" s="8" t="inlineStr">
+      <c r="O35" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4148,20 +4148,20 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M36" s="7" t="n">
+      <c r="M36" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -4169,7 +4169,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O36" s="8" t="inlineStr">
+      <c r="O36" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4245,20 +4245,20 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M37" s="7" t="n">
+      <c r="M37" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -4266,7 +4266,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O37" s="8" t="inlineStr">
+      <c r="O37" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4342,20 +4342,20 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="8" t="inlineStr">
+        <v>-18</v>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M38" s="7" t="n">
+      <c r="M38" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -4363,7 +4363,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O38" s="8" t="inlineStr">
+      <c r="O38" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4439,20 +4439,20 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M39" s="7" t="n">
+      <c r="M39" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -4460,7 +4460,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O39" s="8" t="inlineStr">
+      <c r="O39" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4484,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -4536,20 +4536,20 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M40" s="7" t="n">
+      <c r="M40" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -4557,7 +4557,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O40" s="8" t="inlineStr">
+      <c r="O40" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4633,20 +4633,20 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M41" s="7" t="n">
+      <c r="M41" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4654,7 +4654,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O41" s="8" t="inlineStr">
+      <c r="O41" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4730,20 +4730,20 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L42" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M42" s="7" t="n">
+      <c r="M42" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -4751,7 +4751,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O42" s="8" t="inlineStr">
+      <c r="O42" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -4827,20 +4827,20 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L43" s="8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M43" s="7" t="n">
+      <c r="M43" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -4848,7 +4848,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O43" s="8" t="inlineStr">
+      <c r="O43" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4871,8 +4871,8 @@
       <c r="U43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V43" s="9" t="n">
-        <v>3</v>
+      <c r="V43" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -4924,20 +4924,20 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M44" s="7" t="n">
+      <c r="M44" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -4945,7 +4945,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O44" s="8" t="inlineStr">
+      <c r="O44" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="X44" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y44" s="9" t="n">
         <v>0</v>
@@ -5021,20 +5021,20 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M45" s="7" t="n">
+      <c r="M45" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -5042,7 +5042,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O45" s="8" t="inlineStr">
+      <c r="O45" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5118,20 +5118,20 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L46" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M46" s="7" t="n">
+      <c r="M46" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -5139,7 +5139,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O46" s="8" t="inlineStr">
+      <c r="O46" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5148,7 +5148,7 @@
         <v>0</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" s="9" t="n">
         <v>0</v>
@@ -5166,7 +5166,7 @@
         <v>4</v>
       </c>
       <c r="W46" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X46" s="9" t="n">
         <v>1</v>
@@ -5215,20 +5215,20 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M47" s="7" t="n">
+      <c r="M47" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -5236,7 +5236,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O47" s="8" t="inlineStr">
+      <c r="O47" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5320,12 +5320,12 @@
       <c r="K48" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L48" s="8" t="inlineStr">
+      <c r="L48" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M48" s="7" t="n">
+      <c r="M48" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -5333,7 +5333,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O48" s="8" t="inlineStr">
+      <c r="O48" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5357,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -5409,20 +5409,20 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M49" s="7" t="n">
+      <c r="M49" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -5430,7 +5430,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O49" s="8" t="inlineStr">
+      <c r="O49" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5506,20 +5506,20 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L50" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M50" s="7" t="n">
+      <c r="M50" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -5527,7 +5527,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O50" s="8" t="inlineStr">
+      <c r="O50" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5551,7 +5551,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
@@ -5603,20 +5603,20 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L51" s="8" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M51" s="7" t="n">
+      <c r="M51" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -5624,7 +5624,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O51" s="8" t="inlineStr">
+      <c r="O51" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5700,20 +5700,20 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M52" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M52" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -5721,7 +5721,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O52" s="8" t="inlineStr">
+      <c r="O52" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5797,20 +5797,20 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M53" s="7" t="n">
+      <c r="M53" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -5818,7 +5818,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O53" s="8" t="inlineStr">
+      <c r="O53" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5902,12 +5902,12 @@
       <c r="K54" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L54" s="8" t="inlineStr">
+      <c r="L54" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M54" s="7" t="n">
+      <c r="M54" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -5915,7 +5915,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O54" s="8" t="inlineStr">
+      <c r="O54" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5939,7 +5939,7 @@
         <v>0</v>
       </c>
       <c r="V54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W54" s="9" t="n">
         <v>0</v>
@@ -6004,7 +6004,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M55" s="7" t="n">
+      <c r="M55" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -6012,7 +6012,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O55" s="8" t="inlineStr">
+      <c r="O55" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6088,20 +6088,20 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L56" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M56" s="7" t="n">
+      <c r="M56" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -6109,7 +6109,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O56" s="8" t="inlineStr">
+      <c r="O56" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6185,20 +6185,20 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="8" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M57" s="7" t="n">
+      <c r="M57" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -6206,7 +6206,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O57" s="8" t="inlineStr">
+      <c r="O57" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6282,20 +6282,20 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L58" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M58" s="7" t="n">
+      <c r="M58" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N58" s="4" t="inlineStr">
@@ -6303,7 +6303,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O58" s="8" t="inlineStr">
+      <c r="O58" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6379,20 +6379,20 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M59" s="7" t="n">
+      <c r="M59" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -6400,7 +6400,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O59" s="8" t="inlineStr">
+      <c r="O59" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6476,20 +6476,20 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L60" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M60" s="7" t="n">
+      <c r="M60" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -6497,7 +6497,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O60" s="8" t="inlineStr">
+      <c r="O60" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6521,7 +6521,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>0</v>
@@ -6573,20 +6573,20 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L61" s="8" t="inlineStr">
+        <v>-12</v>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M61" s="7" t="n">
+      <c r="M61" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -6594,7 +6594,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O61" s="8" t="inlineStr">
+      <c r="O61" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -6670,20 +6670,20 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M62" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M62" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
@@ -6691,7 +6691,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O62" s="8" t="inlineStr">
+      <c r="O62" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6767,20 +6767,20 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M63" s="7" t="n">
+      <c r="M63" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -6788,7 +6788,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O63" s="8" t="inlineStr">
+      <c r="O63" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6815,7 +6815,7 @@
         <v>4</v>
       </c>
       <c r="W63" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X63" s="9" t="n">
         <v>1</v>
@@ -6872,12 +6872,12 @@
       <c r="K64" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L64" s="8" t="inlineStr">
+      <c r="L64" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M64" s="7" t="n">
+      <c r="M64" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N64" s="4" t="inlineStr">
@@ -6885,7 +6885,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O64" s="8" t="inlineStr">
+      <c r="O64" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6961,20 +6961,20 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M65" s="7" t="n">
+      <c r="M65" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -6982,7 +6982,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O65" s="8" t="inlineStr">
+      <c r="O65" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7058,20 +7058,20 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M66" s="7" t="n">
+      <c r="M66" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N66" s="4" t="inlineStr">
@@ -7079,7 +7079,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O66" s="8" t="inlineStr">
+      <c r="O66" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7155,20 +7155,20 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L67" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M67" s="7" t="n">
+      <c r="M67" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N67" s="4" t="inlineStr">
@@ -7176,7 +7176,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O67" s="8" t="inlineStr">
+      <c r="O67" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7200,7 +7200,7 @@
         <v>3</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7252,20 +7252,20 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M68" s="7" t="n">
+      <c r="M68" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N68" s="4" t="inlineStr">
@@ -7273,7 +7273,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O68" s="8" t="inlineStr">
+      <c r="O68" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7349,20 +7349,20 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L69" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M69" s="7" t="n">
+      <c r="M69" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N69" s="4" t="inlineStr">
@@ -7370,7 +7370,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O69" s="8" t="inlineStr">
+      <c r="O69" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7394,7 +7394,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7446,20 +7446,20 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M70" s="7" t="n">
+      <c r="M70" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N70" s="4" t="inlineStr">
@@ -7467,7 +7467,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O70" s="8" t="inlineStr">
+      <c r="O70" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7543,20 +7543,20 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M71" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M71" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -7564,7 +7564,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O71" s="8" t="inlineStr">
+      <c r="O71" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7640,20 +7640,20 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L72" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M72" s="7" t="n">
+      <c r="M72" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N72" s="4" t="inlineStr">
@@ -7661,7 +7661,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O72" s="8" t="inlineStr">
+      <c r="O72" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7737,20 +7737,20 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="8" t="inlineStr">
+        <v>-18</v>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M73" s="7" t="n">
+      <c r="M73" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -7758,7 +7758,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O73" s="8" t="inlineStr">
+      <c r="O73" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7834,20 +7834,20 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M74" s="7" t="n">
+      <c r="M74" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
@@ -7855,7 +7855,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O74" s="8" t="inlineStr">
+      <c r="O74" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7931,20 +7931,20 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M75" s="7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M75" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N75" s="4" t="inlineStr">
@@ -7952,7 +7952,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O75" s="8" t="inlineStr">
+      <c r="O75" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7967,7 +7967,7 @@
         <v>0</v>
       </c>
       <c r="S75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T75" s="9" t="n">
         <v>0</v>
@@ -8028,20 +8028,20 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L76" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M76" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L76" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M76" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N76" s="4" t="inlineStr">
@@ -8049,7 +8049,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O76" s="8" t="inlineStr">
+      <c r="O76" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8125,20 +8125,20 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M77" s="7" t="n">
+      <c r="M77" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N77" s="4" t="inlineStr">
@@ -8146,13 +8146,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O77" s="8" t="inlineStr">
+      <c r="O77" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q77" s="9" t="n">
         <v>0</v>
@@ -8222,20 +8222,20 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L78" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M78" s="7" t="n">
+      <c r="M78" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N78" s="4" t="inlineStr">
@@ -8243,7 +8243,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O78" s="8" t="inlineStr">
+      <c r="O78" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8267,7 +8267,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -8319,20 +8319,20 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M79" s="7" t="n">
+      <c r="M79" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N79" s="4" t="inlineStr">
@@ -8340,7 +8340,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O79" s="8" t="inlineStr">
+      <c r="O79" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8416,20 +8416,20 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M80" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L80" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M80" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N80" s="4" t="inlineStr">
@@ -8437,7 +8437,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O80" s="8" t="inlineStr">
+      <c r="O80" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8513,20 +8513,20 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M81" s="7" t="n">
+      <c r="M81" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N81" s="4" t="inlineStr">
@@ -8534,7 +8534,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O81" s="8" t="inlineStr">
+      <c r="O81" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8610,20 +8610,20 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L82" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M82" s="7" t="n">
+      <c r="M82" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N82" s="4" t="inlineStr">
@@ -8631,7 +8631,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O82" s="8" t="inlineStr">
+      <c r="O82" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8707,20 +8707,20 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L83" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M83" s="7" t="n">
+      <c r="M83" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N83" s="4" t="inlineStr">
@@ -8728,7 +8728,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O83" s="8" t="inlineStr">
+      <c r="O83" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8804,20 +8804,20 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L84" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M84" s="7" t="n">
+      <c r="M84" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N84" s="4" t="inlineStr">
@@ -8825,7 +8825,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O84" s="8" t="inlineStr">
+      <c r="O84" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8909,12 +8909,12 @@
       <c r="K85" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L85" s="8" t="inlineStr">
+      <c r="L85" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M85" s="7" t="n">
+      <c r="M85" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N85" s="4" t="inlineStr">
@@ -8922,7 +8922,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O85" s="8" t="inlineStr">
+      <c r="O85" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8946,7 +8946,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -8998,20 +8998,20 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M86" s="7" t="n">
+      <c r="M86" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N86" s="4" t="inlineStr">
@@ -9019,7 +9019,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O86" s="8" t="inlineStr">
+      <c r="O86" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9046,7 +9046,7 @@
         <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X86" s="10" t="n">
         <v>7</v>
@@ -9095,20 +9095,20 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M87" s="7" t="n">
+      <c r="M87" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N87" s="4" t="inlineStr">
@@ -9116,7 +9116,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O87" s="8" t="inlineStr">
+      <c r="O87" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9192,20 +9192,20 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L88" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L88" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M88" s="7" t="n">
+      <c r="M88" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N88" s="4" t="inlineStr">
@@ -9213,7 +9213,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O88" s="8" t="inlineStr">
+      <c r="O88" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9289,20 +9289,20 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M89" s="7" t="n">
+      <c r="M89" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N89" s="4" t="inlineStr">
@@ -9310,7 +9310,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O89" s="8" t="inlineStr">
+      <c r="O89" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9386,20 +9386,20 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L90" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M90" s="7" t="n">
+      <c r="M90" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N90" s="4" t="inlineStr">
@@ -9407,7 +9407,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O90" s="8" t="inlineStr">
+      <c r="O90" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9491,12 +9491,12 @@
       <c r="K91" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L91" s="8" t="inlineStr">
+      <c r="L91" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M91" s="7" t="n">
+      <c r="M91" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N91" s="4" t="inlineStr">
@@ -9504,7 +9504,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O91" s="8" t="inlineStr">
+      <c r="O91" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9580,20 +9580,20 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M92" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M92" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N92" s="4" t="inlineStr">
@@ -9601,7 +9601,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O92" s="8" t="inlineStr">
+      <c r="O92" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9677,20 +9677,20 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M93" s="7" t="n">
+      <c r="M93" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N93" s="4" t="inlineStr">
@@ -9698,7 +9698,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O93" s="8" t="inlineStr">
+      <c r="O93" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9722,7 +9722,7 @@
         <v>0</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
@@ -9782,12 +9782,12 @@
       <c r="K94" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L94" s="8" t="inlineStr">
+      <c r="L94" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M94" s="7" t="n">
+      <c r="M94" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N94" s="4" t="inlineStr">
@@ -9795,7 +9795,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O94" s="8" t="inlineStr">
+      <c r="O94" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9871,20 +9871,20 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L95" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M95" s="7" t="n">
+      <c r="M95" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N95" s="4" t="inlineStr">
@@ -9892,7 +9892,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O95" s="8" t="inlineStr">
+      <c r="O95" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9968,20 +9968,20 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L96" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M96" s="7" t="n">
+      <c r="M96" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N96" s="4" t="inlineStr">
@@ -9989,7 +9989,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O96" s="8" t="inlineStr">
+      <c r="O96" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10065,20 +10065,20 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L97" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M97" s="7" t="n">
+      <c r="M97" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N97" s="4" t="inlineStr">
@@ -10086,7 +10086,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O97" s="8" t="inlineStr">
+      <c r="O97" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10162,20 +10162,20 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L98" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M98" s="7" t="n">
+      <c r="M98" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N98" s="4" t="inlineStr">
@@ -10183,7 +10183,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O98" s="8" t="inlineStr">
+      <c r="O98" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10259,20 +10259,20 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L99" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M99" s="7" t="n">
+      <c r="M99" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N99" s="4" t="inlineStr">
@@ -10280,7 +10280,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O99" s="8" t="inlineStr">
+      <c r="O99" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10356,20 +10356,20 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M100" s="7" t="n">
+      <c r="M100" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N100" s="4" t="inlineStr">
@@ -10377,7 +10377,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O100" s="8" t="inlineStr">
+      <c r="O100" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10453,20 +10453,20 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L101" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M101" s="7" t="n">
+      <c r="M101" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N101" s="4" t="inlineStr">
@@ -10474,7 +10474,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O101" s="8" t="inlineStr">
+      <c r="O101" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10550,20 +10550,20 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M102" s="7" t="n">
+        <v>-23</v>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M102" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
@@ -10571,7 +10571,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O102" s="8" t="inlineStr">
+      <c r="O102" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10647,20 +10647,20 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M103" s="7" t="n">
+      <c r="M103" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N103" s="4" t="inlineStr">
@@ -10668,7 +10668,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O103" s="8" t="inlineStr">
+      <c r="O103" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10744,20 +10744,20 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M104" s="7" t="n">
+      <c r="M104" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N104" s="4" t="inlineStr">
@@ -10765,7 +10765,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O104" s="8" t="inlineStr">
+      <c r="O104" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10841,20 +10841,20 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M105" s="7" t="n">
+      <c r="M105" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N105" s="4" t="inlineStr">
@@ -10862,7 +10862,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O105" s="8" t="inlineStr">
+      <c r="O105" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -10938,20 +10938,20 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M106" s="7" t="n">
+      <c r="M106" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N106" s="4" t="inlineStr">
@@ -10959,7 +10959,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O106" s="8" t="inlineStr">
+      <c r="O106" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10982,8 +10982,8 @@
       <c r="U106" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V106" s="9" t="n">
-        <v>1</v>
+      <c r="V106" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
@@ -11035,20 +11035,20 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M107" s="7" t="n">
+      <c r="M107" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N107" s="4" t="inlineStr">
@@ -11056,7 +11056,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O107" s="8" t="inlineStr">
+      <c r="O107" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11132,20 +11132,20 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="8" t="inlineStr">
+        <v>-11</v>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M108" s="7" t="n">
+      <c r="M108" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N108" s="4" t="inlineStr">
@@ -11153,7 +11153,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O108" s="8" t="inlineStr">
+      <c r="O108" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11229,20 +11229,20 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L109" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M109" s="7" t="n">
+      <c r="M109" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N109" s="4" t="inlineStr">
@@ -11250,7 +11250,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O109" s="8" t="inlineStr">
+      <c r="O109" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11326,20 +11326,20 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M110" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L110" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M110" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N110" s="4" t="inlineStr">
@@ -11347,7 +11347,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O110" s="8" t="inlineStr">
+      <c r="O110" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11362,7 +11362,7 @@
         <v>0</v>
       </c>
       <c r="S110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T110" s="9" t="n">
         <v>0</v>
@@ -11423,20 +11423,20 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L111" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M111" s="7" t="n">
+      <c r="M111" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N111" s="4" t="inlineStr">
@@ -11444,7 +11444,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O111" s="8" t="inlineStr">
+      <c r="O111" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11468,7 +11468,7 @@
         <v>0</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -11520,20 +11520,20 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M112" s="7" t="n">
+        <v>-12</v>
+      </c>
+      <c r="L112" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M112" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N112" s="4" t="inlineStr">
@@ -11541,7 +11541,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O112" s="8" t="inlineStr">
+      <c r="O112" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11617,20 +11617,20 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L113" s="8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L113" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M113" s="7" t="n">
+      <c r="M113" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N113" s="4" t="inlineStr">
@@ -11638,7 +11638,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O113" s="8" t="inlineStr">
+      <c r="O113" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11714,20 +11714,20 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L114" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M114" s="7" t="n">
+      <c r="M114" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N114" s="4" t="inlineStr">
@@ -11735,7 +11735,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O114" s="8" t="inlineStr">
+      <c r="O114" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11764,8 +11764,8 @@
       <c r="W114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X114" s="9" t="n">
-        <v>1</v>
+      <c r="X114" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y114" s="9" t="n">
         <v>0</v>
@@ -11811,20 +11811,20 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L115" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M115" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L115" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M115" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N115" s="4" t="inlineStr">
@@ -11832,7 +11832,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O115" s="8" t="inlineStr">
+      <c r="O115" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11908,20 +11908,20 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L116" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L116" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M116" s="7" t="n">
+      <c r="M116" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N116" s="4" t="inlineStr">
@@ -11929,7 +11929,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O116" s="8" t="inlineStr">
+      <c r="O116" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11953,7 +11953,7 @@
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
@@ -12005,20 +12005,20 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M117" s="7" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L117" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M117" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N117" s="4" t="inlineStr">
@@ -12026,7 +12026,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O117" s="8" t="inlineStr">
+      <c r="O117" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12102,20 +12102,20 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M118" s="7" t="n">
+      <c r="M118" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N118" s="4" t="inlineStr">
@@ -12123,7 +12123,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O118" s="8" t="inlineStr">
+      <c r="O118" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12152,8 +12152,8 @@
       <c r="W118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X118" s="9" t="n">
-        <v>3</v>
+      <c r="X118" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
@@ -12199,20 +12199,20 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M119" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L119" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M119" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N119" s="4" t="inlineStr">
@@ -12220,7 +12220,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O119" s="8" t="inlineStr">
+      <c r="O119" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12296,20 +12296,20 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L120" s="8" t="inlineStr">
+        <v>-12</v>
+      </c>
+      <c r="L120" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M120" s="7" t="n">
+      <c r="M120" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N120" s="4" t="inlineStr">
@@ -12317,7 +12317,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O120" s="8" t="inlineStr">
+      <c r="O120" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12393,20 +12393,20 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M121" s="7" t="n">
+      <c r="M121" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N121" s="4" t="inlineStr">
@@ -12414,7 +12414,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O121" s="8" t="inlineStr">
+      <c r="O121" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12490,20 +12490,20 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L122" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L122" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M122" s="7" t="n">
+      <c r="M122" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N122" s="4" t="inlineStr">
@@ -12511,7 +12511,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O122" s="8" t="inlineStr">
+      <c r="O122" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12587,20 +12587,20 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L123" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L123" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M123" s="7" t="n">
+      <c r="M123" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N123" s="4" t="inlineStr">
@@ -12608,7 +12608,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O123" s="8" t="inlineStr">
+      <c r="O123" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12684,20 +12684,20 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L124" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M124" s="7" t="n">
+      <c r="M124" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N124" s="4" t="inlineStr">
@@ -12705,7 +12705,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O124" s="8" t="inlineStr">
+      <c r="O124" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12781,20 +12781,20 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L125" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L125" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M125" s="7" t="n">
+      <c r="M125" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N125" s="4" t="inlineStr">
@@ -12802,7 +12802,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O125" s="8" t="inlineStr">
+      <c r="O125" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12829,7 +12829,7 @@
         <v>4</v>
       </c>
       <c r="W125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X125" s="9" t="n">
         <v>3</v>
@@ -12878,20 +12878,20 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L126" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L126" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M126" s="7" t="n">
+      <c r="M126" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N126" s="4" t="inlineStr">
@@ -12899,7 +12899,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O126" s="8" t="inlineStr">
+      <c r="O126" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12929,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="X126" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
@@ -13044,7 +13044,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -13095,7 +13095,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -13110,7 +13110,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -13176,7 +13176,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -13209,7 +13209,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -13293,7 +13293,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -13341,7 +13341,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -13407,7 +13407,7 @@
         <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -13473,7 +13473,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -13506,7 +13506,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -13539,7 +13539,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -13605,7 +13605,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -13671,7 +13671,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -13689,7 +13689,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -13737,7 +13737,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -13770,7 +13770,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -13803,7 +13803,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">

--- a/docs/d/212/inyear.xlsx
+++ b/docs/d/212/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/212/inyear.xlsx
+++ b/docs/d/212/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/212/inyear.xlsx
+++ b/docs/d/212/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/212/inyear.xlsx
+++ b/docs/d/212/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/212/inyear.xlsx
+++ b/docs/d/212/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 8 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 8 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 38 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 38 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>4</v>
       </c>
       <c r="W2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" s="10" t="n">
         <v>4</v>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="P7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="9" t="n">
         <v>0</v>
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>0</v>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="P30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30" s="9" t="n">
         <v>0</v>
@@ -4566,7 +4566,7 @@
         <v>1</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" s="9" t="n">
         <v>0</v>
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         </is>
       </c>
       <c r="P49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q49" s="9" t="n">
         <v>0</v>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6476,13 +6476,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8163,8 +8163,8 @@
       <c r="S77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T77" s="9" t="n">
-        <v>0</v>
+      <c r="T77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U77" s="9" t="n">
         <v>0</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         </is>
       </c>
       <c r="P88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q88" s="9" t="n">
         <v>1</v>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -11035,13 +11035,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         <v>4</v>
       </c>
       <c r="W107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X107" s="10" t="n">
         <v>5</v>
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -11855,8 +11855,8 @@
       <c r="U115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V115" s="9" t="n">
-        <v>2</v>
+      <c r="V115" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
@@ -12296,13 +12296,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -12831,8 +12831,8 @@
       <c r="W125" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="X125" s="9" t="n">
-        <v>3</v>
+      <c r="X125" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
@@ -12928,8 +12928,8 @@
       <c r="W126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X126" s="9" t="n">
-        <v>3</v>
+      <c r="X126" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
@@ -13491,7 +13491,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>

--- a/docs/d/212/inyear.xlsx
+++ b/docs/d/212/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 8 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 8 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 38 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 38 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -3372,13 +3372,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-15</v>
+        <v>-2</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
@@ -3469,13 +3469,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7199,8 +7199,8 @@
       <c r="U67" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="V67" s="9" t="n">
-        <v>3</v>
+      <c r="V67" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8072,8 +8072,8 @@
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="9" t="n">
-        <v>3</v>
+      <c r="V76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>1</v>
       </c>
       <c r="Q83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R83" s="9" t="n">
         <v>0</v>
@@ -8745,8 +8745,8 @@
       <c r="S83" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T83" s="9" t="n">
-        <v>0</v>
+      <c r="T83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U83" s="9" t="n">
         <v>0</v>
@@ -9001,10 +9001,10 @@
         <v>38</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -11811,17 +11811,17 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L115" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L115" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M115" s="8" t="n">
@@ -11859,7 +11859,7 @@
         <v>4</v>
       </c>
       <c r="W115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X115" s="10" t="n">
         <v>5</v>
@@ -12296,13 +12296,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13491,7 +13491,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13524,7 +13524,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13770,7 +13770,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
